--- a/job_application_forms/049_tech_ux_designer_employment_application--job_application_forms.xlsx
+++ b/job_application_forms/049_tech_ux_designer_employment_application--job_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -665,8 +665,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="49" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -694,12 +694,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'email',_'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'email', 'value': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -711,12 +711,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'phone',_'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'phone', 'value': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -728,12 +728,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'company_1',_'value':_'company_1'}</t>
+          <t>company_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'company_1', 'value': 'Company 1'}</t>
+          <t>Company 1</t>
         </is>
       </c>
     </row>
@@ -745,12 +745,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'job_title_1',_'value':_'job_title_1'}</t>
+          <t>job_title_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'job_title_1', 'value': 'Job Title 1'}</t>
+          <t>Job Title 1</t>
         </is>
       </c>
     </row>
@@ -762,12 +762,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'location_1',_'value':_'location_1'}</t>
+          <t>location_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'location_1', 'value': 'Location 1'}</t>
+          <t>Location 1</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'duration_1',_'value':_'duration_1'}</t>
+          <t>duration_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'duration_1', 'value': 'Duration 1'}</t>
+          <t>Duration 1</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'company_2',_'value':_'company_2'}</t>
+          <t>company_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'company_2', 'value': 'Company 2'}</t>
+          <t>Company 2</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'job_title_2',_'value':_'job_title_2'}</t>
+          <t>job_title_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'job_title_2', 'value': 'Job Title 2'}</t>
+          <t>Job Title 2</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'location_2',_'value':_'location_2'}</t>
+          <t>location_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'location_2', 'value': 'Location 2'}</t>
+          <t>Location 2</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'duration_2',_'value':_'duration_2'}</t>
+          <t>duration_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'duration_2', 'value': 'Duration 2'}</t>
+          <t>Duration 2</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_'company_3',_'value':_'company_3'}</t>
+          <t>company_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': 'company_3', 'value': 'Company 3'}</t>
+          <t>Company 3</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'name':_'job_title_3',_'value':_'job_title_3'}</t>
+          <t>job_title_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'name': 'job_title_3', 'value': 'Job Title 3'}</t>
+          <t>Job Title 3</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'name':_'location_3',_'value':_'location_3'}</t>
+          <t>location_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'name': 'location_3', 'value': 'Location 3'}</t>
+          <t>Location 3</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'name':_'duration_3',_'value':_'duration_3'}</t>
+          <t>duration_3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'name': 'duration_3', 'value': 'Duration 3'}</t>
+          <t>Duration 3</t>
         </is>
       </c>
     </row>
